--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.15.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.15.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.15.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.15.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="53" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œpurpos</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Estate â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]8</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]8</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L35: isolated marker/symbol line :: 0</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L105: symbol-only separator/garbage line :: - . . 2</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]8</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -658,12 +662,12 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Estate €</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -671,7 +675,11 @@
           <t>L51: isolated marker/symbol line :: e</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L105: symbol-only separator/garbage line :: - . . 2</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
@@ -711,7 +719,7 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
@@ -734,12 +742,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -937,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -981,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1020,7 +1028,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
